--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-humanname.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-humanname.xlsx
@@ -350,7 +350,7 @@
     <t>nameRepresentationUse</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-EN-representation}
+    <t xml:space="preserve">Extension {iso21090-EN-representation|5.2.0}
 </t>
   </si>
   <si>
@@ -849,7 +849,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="33.2265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="37.7578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-humanname.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-humanname.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/HumanName</t>
+    <t>http://hl7.org/fhir/StructureDefinition/HumanName|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-humanname.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-humanname.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/HumanName|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/HumanName</t>
   </si>
   <si>
     <t>Abstract</t>
